--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{768A0ADB-CE89-418B-9905-61079C097D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA05F6F6-4D2D-4D2C-B384-FE205885AFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="49">
   <si>
     <t>Όνομα μέλους</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>ARISTON Wash &amp; Dry (Members)</t>
+  </si>
+  <si>
+    <t>ΑΡΗΣ ΚΑΡΠΑΘΙΟΥ</t>
+  </si>
+  <si>
+    <t>ariskarpathiou@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -935,7 +941,7 @@
         <v>46032</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>32</v>
@@ -1346,13 +1352,21 @@
       <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
+      <c r="D18" s="8">
+        <v>46033</v>
+      </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="11" t="s">
+        <v>48</v>
+      </c>
       <c r="G18" t="s">
         <v>30</v>
       </c>
@@ -4855,15 +4869,16 @@
     <hyperlink ref="A15" r:id="rId12" display="https://aristonwashdry.gr/admin/users/14" xr:uid="{736FE863-340D-447B-BE11-4D0BD77A39B9}"/>
     <hyperlink ref="A16" r:id="rId13" display="https://aristonwashdry.gr/admin/users/15" xr:uid="{A60A9E79-52B6-4C45-AAE9-22063D34C753}"/>
     <hyperlink ref="A17" r:id="rId14" display="https://aristonwashdry.gr/admin/users/16" xr:uid="{EB7BD8CD-34F7-45FC-9EB0-76870B9D66D9}"/>
+    <hyperlink ref="A18" r:id="rId15" display="https://aristonwashdry.gr/admin/users/17" xr:uid="{287FD2B1-A1A7-4F9B-95C9-BB67B74AB67F}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId15"/>
+  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId16"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA05F6F6-4D2D-4D2C-B384-FE205885AFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E2EF77-E984-48B1-A139-178A40799F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="55">
   <si>
     <t>Όνομα μέλους</t>
   </si>
@@ -174,6 +174,24 @@
   </si>
   <si>
     <t>ariskarpathiou@gmail.com</t>
+  </si>
+  <si>
+    <t>Μαρία Γεροχειμώνα</t>
+  </si>
+  <si>
+    <t>Βασίλης Σαμιώτης</t>
+  </si>
+  <si>
+    <t>Στέλλα Μαργαριτη</t>
+  </si>
+  <si>
+    <t>mariagerocheimona_12@icloud.com</t>
+  </si>
+  <si>
+    <t>vsamiotis09@gmail.com</t>
+  </si>
+  <si>
+    <t>margaritiistella368@outlook.com</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1369,7 @@
       </c>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>47</v>
       </c>
@@ -1378,14 +1396,22 @@
       </c>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="C19" t="s">
         <v>30</v>
       </c>
+      <c r="D19" s="8">
+        <v>46034</v>
+      </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="G19" t="s">
         <v>30</v>
       </c>
@@ -1397,14 +1423,22 @@
       </c>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="C20" t="s">
         <v>30</v>
       </c>
+      <c r="D20" s="8">
+        <v>46034</v>
+      </c>
       <c r="E20" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="6"/>
+      <c r="F20" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="G20" t="s">
         <v>30</v>
       </c>
@@ -1417,13 +1451,21 @@
       <c r="L20" s="6"/>
     </row>
     <row r="21" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
+      <c r="D21" s="8">
+        <v>46034</v>
+      </c>
       <c r="E21" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="G21" t="s">
         <v>30</v>
       </c>
@@ -4870,15 +4912,18 @@
     <hyperlink ref="A16" r:id="rId13" display="https://aristonwashdry.gr/admin/users/15" xr:uid="{A60A9E79-52B6-4C45-AAE9-22063D34C753}"/>
     <hyperlink ref="A17" r:id="rId14" display="https://aristonwashdry.gr/admin/users/16" xr:uid="{EB7BD8CD-34F7-45FC-9EB0-76870B9D66D9}"/>
     <hyperlink ref="A18" r:id="rId15" display="https://aristonwashdry.gr/admin/users/17" xr:uid="{287FD2B1-A1A7-4F9B-95C9-BB67B74AB67F}"/>
+    <hyperlink ref="A19" r:id="rId16" display="https://aristonwashdry.gr/admin/users/18" xr:uid="{F4A2EBE6-FF22-4EDC-992D-D2B3F65000A1}"/>
+    <hyperlink ref="A20" r:id="rId17" display="https://aristonwashdry.gr/admin/users/19" xr:uid="{CE1D70E6-FBF5-43BC-A9FD-801279D120D7}"/>
+    <hyperlink ref="A21" r:id="rId18" display="https://aristonwashdry.gr/admin/users/20" xr:uid="{F319D8B6-A628-4303-A453-A2A9C096D4E8}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId16"/>
+  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId19"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>
--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E2EF77-E984-48B1-A139-178A40799F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5367C6-4DD8-412E-93F6-8A84D2254215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="56">
   <si>
     <t>Όνομα μέλους</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>margaritiistella368@outlook.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΜΕΛΟΣ </t>
   </si>
 </sst>
 </file>
@@ -928,7 +931,7 @@
         <v>46032</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>31</v>
@@ -990,7 +993,7 @@
         <v>46032</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>33</v>
@@ -1021,7 +1024,7 @@
         <v>46032</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>34</v>
@@ -1052,7 +1055,7 @@
         <v>46032</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>35</v>
@@ -1083,7 +1086,7 @@
         <v>46032</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>36</v>
@@ -1113,7 +1116,7 @@
         <v>46032</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>37</v>
@@ -1143,7 +1146,7 @@
         <v>46032</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>38</v>
@@ -1173,7 +1176,7 @@
         <v>46032</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>39</v>
@@ -1203,7 +1206,7 @@
         <v>46032</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>40</v>
@@ -1233,7 +1236,7 @@
         <v>46032</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>41</v>
@@ -1263,7 +1266,7 @@
         <v>46032</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>42</v>
@@ -1293,7 +1296,7 @@
         <v>46032</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>43</v>
@@ -1323,7 +1326,7 @@
         <v>46033</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>44</v>
@@ -1353,7 +1356,7 @@
         <v>46033</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>45</v>
@@ -1380,7 +1383,7 @@
         <v>46033</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>48</v>
@@ -1407,7 +1410,7 @@
         <v>46034</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>52</v>
@@ -1434,7 +1437,7 @@
         <v>46034</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>53</v>
@@ -1461,7 +1464,7 @@
         <v>46034</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>54</v>
@@ -1482,7 +1485,7 @@
         <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" t="s">
@@ -1501,7 +1504,7 @@
         <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" t="s">
@@ -1520,7 +1523,7 @@
         <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" t="s">
@@ -1539,7 +1542,7 @@
         <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" t="s">
@@ -1558,7 +1561,7 @@
         <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" t="s">
@@ -1577,7 +1580,7 @@
         <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" t="s">
@@ -1596,7 +1599,7 @@
         <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" t="s">
@@ -1615,7 +1618,7 @@
         <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" t="s">
@@ -1634,7 +1637,7 @@
         <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" t="s">
@@ -1653,7 +1656,7 @@
         <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" t="s">
@@ -1672,7 +1675,7 @@
         <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" t="s">
@@ -1691,7 +1694,7 @@
         <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" t="s">
@@ -1710,7 +1713,7 @@
         <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" t="s">
@@ -1729,7 +1732,7 @@
         <v>30</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" t="s">
@@ -1748,7 +1751,7 @@
         <v>30</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" t="s">
@@ -1767,7 +1770,7 @@
         <v>30</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" t="s">
@@ -1786,7 +1789,7 @@
         <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" t="s">
@@ -1805,7 +1808,7 @@
         <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" t="s">
@@ -1824,7 +1827,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" t="s">
@@ -1843,7 +1846,7 @@
         <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" t="s">
@@ -1862,7 +1865,7 @@
         <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" t="s">
@@ -1881,7 +1884,7 @@
         <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" t="s">
@@ -1900,7 +1903,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" t="s">
@@ -1919,7 +1922,7 @@
         <v>30</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" t="s">
@@ -1938,7 +1941,7 @@
         <v>30</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" t="s">
@@ -1957,7 +1960,7 @@
         <v>30</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" t="s">
@@ -1976,7 +1979,7 @@
         <v>30</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" t="s">
@@ -1995,7 +1998,7 @@
         <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" t="s">
@@ -2014,7 +2017,7 @@
         <v>30</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" t="s">
@@ -2033,7 +2036,7 @@
         <v>30</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" t="s">
@@ -2052,7 +2055,7 @@
         <v>30</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" t="s">
@@ -2071,7 +2074,7 @@
         <v>30</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" t="s">
@@ -2090,7 +2093,7 @@
         <v>30</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" t="s">
@@ -2109,7 +2112,7 @@
         <v>30</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" t="s">
@@ -2128,7 +2131,7 @@
         <v>30</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" t="s">
@@ -2147,7 +2150,7 @@
         <v>30</v>
       </c>
       <c r="E57" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" t="s">
@@ -2166,7 +2169,7 @@
         <v>30</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" t="s">
@@ -2185,7 +2188,7 @@
         <v>30</v>
       </c>
       <c r="E59" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" t="s">
@@ -2204,7 +2207,7 @@
         <v>30</v>
       </c>
       <c r="E60" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" t="s">
@@ -2223,7 +2226,7 @@
         <v>30</v>
       </c>
       <c r="E61" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" t="s">
@@ -2242,7 +2245,7 @@
         <v>30</v>
       </c>
       <c r="E62" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" t="s">
@@ -2261,7 +2264,7 @@
         <v>30</v>
       </c>
       <c r="E63" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" t="s">
@@ -2280,7 +2283,7 @@
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" t="s">
@@ -2299,7 +2302,7 @@
         <v>30</v>
       </c>
       <c r="E65" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" t="s">
@@ -2318,7 +2321,7 @@
         <v>30</v>
       </c>
       <c r="E66" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" t="s">
@@ -2337,7 +2340,7 @@
         <v>30</v>
       </c>
       <c r="E67" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" t="s">
@@ -2356,7 +2359,7 @@
         <v>30</v>
       </c>
       <c r="E68" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" t="s">
@@ -2375,7 +2378,7 @@
         <v>30</v>
       </c>
       <c r="E69" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" t="s">
@@ -2394,7 +2397,7 @@
         <v>30</v>
       </c>
       <c r="E70" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" t="s">
@@ -2413,7 +2416,7 @@
         <v>30</v>
       </c>
       <c r="E71" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" t="s">
@@ -2432,7 +2435,7 @@
         <v>30</v>
       </c>
       <c r="E72" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" t="s">
@@ -2451,7 +2454,7 @@
         <v>30</v>
       </c>
       <c r="E73" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" t="s">
@@ -2470,7 +2473,7 @@
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" t="s">
@@ -2489,7 +2492,7 @@
         <v>30</v>
       </c>
       <c r="E75" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" t="s">
@@ -2508,7 +2511,7 @@
         <v>30</v>
       </c>
       <c r="E76" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" t="s">
@@ -2527,7 +2530,7 @@
         <v>30</v>
       </c>
       <c r="E77" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" t="s">
@@ -2546,7 +2549,7 @@
         <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" t="s">
@@ -2565,7 +2568,7 @@
         <v>30</v>
       </c>
       <c r="E79" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" t="s">
@@ -2584,7 +2587,7 @@
         <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" t="s">
@@ -2603,7 +2606,7 @@
         <v>30</v>
       </c>
       <c r="E81" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" t="s">
@@ -2622,7 +2625,7 @@
         <v>30</v>
       </c>
       <c r="E82" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" t="s">
@@ -2641,7 +2644,7 @@
         <v>30</v>
       </c>
       <c r="E83" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" t="s">
@@ -2660,7 +2663,7 @@
         <v>30</v>
       </c>
       <c r="E84" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" t="s">
@@ -2679,7 +2682,7 @@
         <v>30</v>
       </c>
       <c r="E85" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" t="s">
@@ -2698,7 +2701,7 @@
         <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" t="s">
@@ -2717,7 +2720,7 @@
         <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" t="s">
@@ -2736,7 +2739,7 @@
         <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" t="s">
@@ -2755,7 +2758,7 @@
         <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" t="s">
@@ -2774,7 +2777,7 @@
         <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" t="s">
@@ -2793,7 +2796,7 @@
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" t="s">
@@ -2812,7 +2815,7 @@
         <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" t="s">
@@ -2831,7 +2834,7 @@
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" t="s">
@@ -2850,7 +2853,7 @@
         <v>30</v>
       </c>
       <c r="E94" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" t="s">
@@ -2869,7 +2872,7 @@
         <v>30</v>
       </c>
       <c r="E95" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F95" s="6"/>
       <c r="G95" t="s">
@@ -2888,7 +2891,7 @@
         <v>30</v>
       </c>
       <c r="E96" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" t="s">
@@ -2907,7 +2910,7 @@
         <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" t="s">
@@ -2926,7 +2929,7 @@
         <v>30</v>
       </c>
       <c r="E98" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F98" s="6"/>
       <c r="G98" t="s">
@@ -2945,7 +2948,7 @@
         <v>30</v>
       </c>
       <c r="E99" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F99" s="6"/>
       <c r="G99" t="s">
@@ -2964,7 +2967,7 @@
         <v>30</v>
       </c>
       <c r="E100" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F100" s="6"/>
       <c r="G100" t="s">
@@ -2983,7 +2986,7 @@
         <v>30</v>
       </c>
       <c r="E101" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F101" s="6"/>
       <c r="G101" t="s">
@@ -3002,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="E102" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F102" s="6"/>
       <c r="G102" t="s">
@@ -3021,7 +3024,7 @@
         <v>30</v>
       </c>
       <c r="E103" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F103" s="6"/>
       <c r="G103" t="s">
@@ -3040,7 +3043,7 @@
         <v>30</v>
       </c>
       <c r="E104" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F104" s="6"/>
       <c r="G104" t="s">
@@ -3059,7 +3062,7 @@
         <v>30</v>
       </c>
       <c r="E105" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" t="s">
@@ -3078,7 +3081,7 @@
         <v>30</v>
       </c>
       <c r="E106" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" t="s">
@@ -3097,7 +3100,7 @@
         <v>30</v>
       </c>
       <c r="E107" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F107" s="6"/>
       <c r="G107" t="s">
@@ -3116,7 +3119,7 @@
         <v>30</v>
       </c>
       <c r="E108" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F108" s="6"/>
       <c r="G108" t="s">
@@ -3135,7 +3138,7 @@
         <v>30</v>
       </c>
       <c r="E109" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F109" s="6"/>
       <c r="G109" t="s">
@@ -3154,7 +3157,7 @@
         <v>30</v>
       </c>
       <c r="E110" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F110" s="6"/>
       <c r="G110" t="s">
@@ -3173,7 +3176,7 @@
         <v>30</v>
       </c>
       <c r="E111" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F111" s="6"/>
       <c r="G111" t="s">
@@ -3192,7 +3195,7 @@
         <v>30</v>
       </c>
       <c r="E112" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F112" s="6"/>
       <c r="G112" t="s">
@@ -3211,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="E113" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F113" s="6"/>
       <c r="G113" t="s">
@@ -3230,7 +3233,7 @@
         <v>30</v>
       </c>
       <c r="E114" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" t="s">
@@ -3249,7 +3252,7 @@
         <v>30</v>
       </c>
       <c r="E115" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" t="s">
@@ -3268,7 +3271,7 @@
         <v>30</v>
       </c>
       <c r="E116" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" t="s">
@@ -3287,7 +3290,7 @@
         <v>30</v>
       </c>
       <c r="E117" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" t="s">
@@ -3306,7 +3309,7 @@
         <v>30</v>
       </c>
       <c r="E118" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" t="s">
@@ -3325,7 +3328,7 @@
         <v>30</v>
       </c>
       <c r="E119" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" t="s">
@@ -3344,7 +3347,7 @@
         <v>30</v>
       </c>
       <c r="E120" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" t="s">
@@ -3363,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="E121" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" t="s">
@@ -3382,7 +3385,7 @@
         <v>30</v>
       </c>
       <c r="E122" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" t="s">
@@ -3401,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="E123" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" t="s">
@@ -3420,7 +3423,7 @@
         <v>30</v>
       </c>
       <c r="E124" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F124" s="6"/>
       <c r="G124" t="s">
@@ -3439,7 +3442,7 @@
         <v>30</v>
       </c>
       <c r="E125" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" t="s">
@@ -3458,7 +3461,7 @@
         <v>30</v>
       </c>
       <c r="E126" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F126" s="6"/>
       <c r="G126" t="s">
@@ -3477,7 +3480,7 @@
         <v>30</v>
       </c>
       <c r="E127" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" t="s">
@@ -3496,7 +3499,7 @@
         <v>30</v>
       </c>
       <c r="E128" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F128" s="6"/>
       <c r="G128" t="s">
@@ -3515,7 +3518,7 @@
         <v>30</v>
       </c>
       <c r="E129" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F129" s="6"/>
       <c r="G129" t="s">
@@ -3534,7 +3537,7 @@
         <v>30</v>
       </c>
       <c r="E130" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F130" s="6"/>
       <c r="G130" t="s">
@@ -3553,7 +3556,7 @@
         <v>30</v>
       </c>
       <c r="E131" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F131" s="6"/>
       <c r="G131" t="s">
@@ -3572,7 +3575,7 @@
         <v>30</v>
       </c>
       <c r="E132" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" t="s">
@@ -3591,7 +3594,7 @@
         <v>30</v>
       </c>
       <c r="E133" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" t="s">
@@ -3610,7 +3613,7 @@
         <v>30</v>
       </c>
       <c r="E134" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F134" s="6"/>
       <c r="G134" t="s">
@@ -3629,7 +3632,7 @@
         <v>30</v>
       </c>
       <c r="E135" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F135" s="6"/>
       <c r="G135" t="s">
@@ -3648,7 +3651,7 @@
         <v>30</v>
       </c>
       <c r="E136" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" t="s">
@@ -3667,7 +3670,7 @@
         <v>30</v>
       </c>
       <c r="E137" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F137" s="6"/>
       <c r="G137" t="s">
@@ -3686,7 +3689,7 @@
         <v>30</v>
       </c>
       <c r="E138" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F138" s="6"/>
       <c r="G138" t="s">
@@ -3705,7 +3708,7 @@
         <v>30</v>
       </c>
       <c r="E139" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" t="s">
@@ -3724,7 +3727,7 @@
         <v>30</v>
       </c>
       <c r="E140" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F140" s="6"/>
       <c r="G140" t="s">
@@ -3743,7 +3746,7 @@
         <v>30</v>
       </c>
       <c r="E141" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F141" s="6"/>
       <c r="G141" t="s">
@@ -3762,7 +3765,7 @@
         <v>30</v>
       </c>
       <c r="E142" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" t="s">
@@ -3781,7 +3784,7 @@
         <v>30</v>
       </c>
       <c r="E143" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F143" s="6"/>
       <c r="G143" t="s">
@@ -3800,7 +3803,7 @@
         <v>30</v>
       </c>
       <c r="E144" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F144" s="6"/>
       <c r="G144" t="s">
@@ -3819,7 +3822,7 @@
         <v>30</v>
       </c>
       <c r="E145" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F145" s="6"/>
       <c r="G145" t="s">
@@ -3838,7 +3841,7 @@
         <v>30</v>
       </c>
       <c r="E146" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" t="s">
@@ -3857,7 +3860,7 @@
         <v>30</v>
       </c>
       <c r="E147" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F147" s="6"/>
       <c r="G147" t="s">
@@ -3876,7 +3879,7 @@
         <v>30</v>
       </c>
       <c r="E148" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F148" s="6"/>
       <c r="G148" t="s">
@@ -3895,7 +3898,7 @@
         <v>30</v>
       </c>
       <c r="E149" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F149" s="6"/>
       <c r="G149" t="s">
@@ -3914,7 +3917,7 @@
         <v>30</v>
       </c>
       <c r="E150" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F150" s="6"/>
       <c r="G150" t="s">
@@ -3933,7 +3936,7 @@
         <v>30</v>
       </c>
       <c r="E151" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F151" s="6"/>
       <c r="G151" t="s">
@@ -3952,7 +3955,7 @@
         <v>30</v>
       </c>
       <c r="E152" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F152" s="6"/>
       <c r="G152" t="s">
@@ -3971,7 +3974,7 @@
         <v>30</v>
       </c>
       <c r="E153" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F153" s="6"/>
       <c r="G153" t="s">
@@ -3990,7 +3993,7 @@
         <v>30</v>
       </c>
       <c r="E154" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F154" s="6"/>
       <c r="G154" t="s">
@@ -4009,7 +4012,7 @@
         <v>30</v>
       </c>
       <c r="E155" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F155" s="6"/>
       <c r="G155" t="s">
@@ -4028,7 +4031,7 @@
         <v>30</v>
       </c>
       <c r="E156" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" t="s">
@@ -4047,7 +4050,7 @@
         <v>30</v>
       </c>
       <c r="E157" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F157" s="6"/>
       <c r="G157" t="s">
@@ -4066,7 +4069,7 @@
         <v>30</v>
       </c>
       <c r="E158" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F158" s="6"/>
       <c r="G158" t="s">
@@ -4085,7 +4088,7 @@
         <v>30</v>
       </c>
       <c r="E159" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F159" s="6"/>
       <c r="G159" t="s">
@@ -4104,7 +4107,7 @@
         <v>30</v>
       </c>
       <c r="E160" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F160" s="6"/>
       <c r="G160" t="s">
@@ -4123,7 +4126,7 @@
         <v>30</v>
       </c>
       <c r="E161" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" t="s">
@@ -4142,7 +4145,7 @@
         <v>30</v>
       </c>
       <c r="E162" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F162" s="6"/>
       <c r="G162" t="s">
@@ -4161,7 +4164,7 @@
         <v>30</v>
       </c>
       <c r="E163" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" t="s">
@@ -4180,7 +4183,7 @@
         <v>30</v>
       </c>
       <c r="E164" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F164" s="6"/>
       <c r="G164" t="s">
@@ -4199,7 +4202,7 @@
         <v>30</v>
       </c>
       <c r="E165" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F165" s="6"/>
       <c r="G165" t="s">
@@ -4218,7 +4221,7 @@
         <v>30</v>
       </c>
       <c r="E166" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" t="s">
@@ -4237,7 +4240,7 @@
         <v>30</v>
       </c>
       <c r="E167" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" t="s">
@@ -4256,7 +4259,7 @@
         <v>30</v>
       </c>
       <c r="E168" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" t="s">
@@ -4275,7 +4278,7 @@
         <v>30</v>
       </c>
       <c r="E169" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F169" s="6"/>
       <c r="G169" t="s">
@@ -4294,7 +4297,7 @@
         <v>30</v>
       </c>
       <c r="E170" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F170" s="6"/>
       <c r="G170" t="s">
@@ -4313,7 +4316,7 @@
         <v>30</v>
       </c>
       <c r="E171" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F171" s="6"/>
       <c r="G171" t="s">
@@ -4332,7 +4335,7 @@
         <v>30</v>
       </c>
       <c r="E172" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F172" s="6"/>
       <c r="G172" t="s">
@@ -4351,7 +4354,7 @@
         <v>30</v>
       </c>
       <c r="E173" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" t="s">
@@ -4370,7 +4373,7 @@
         <v>30</v>
       </c>
       <c r="E174" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" t="s">
@@ -4389,7 +4392,7 @@
         <v>30</v>
       </c>
       <c r="E175" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" t="s">
@@ -4408,7 +4411,7 @@
         <v>30</v>
       </c>
       <c r="E176" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" t="s">
@@ -4427,7 +4430,7 @@
         <v>30</v>
       </c>
       <c r="E177" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" t="s">
@@ -4446,7 +4449,7 @@
         <v>30</v>
       </c>
       <c r="E178" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" t="s">
@@ -4465,7 +4468,7 @@
         <v>30</v>
       </c>
       <c r="E179" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F179" s="6"/>
       <c r="G179" t="s">
@@ -4484,7 +4487,7 @@
         <v>30</v>
       </c>
       <c r="E180" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" t="s">
@@ -4503,7 +4506,7 @@
         <v>30</v>
       </c>
       <c r="E181" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" t="s">
@@ -4522,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="E182" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F182" s="6"/>
       <c r="G182" t="s">
@@ -4541,7 +4544,7 @@
         <v>30</v>
       </c>
       <c r="E183" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F183" s="6"/>
       <c r="G183" t="s">
@@ -4560,7 +4563,7 @@
         <v>30</v>
       </c>
       <c r="E184" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F184" s="6"/>
       <c r="G184" t="s">
@@ -4579,7 +4582,7 @@
         <v>30</v>
       </c>
       <c r="E185" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F185" s="6"/>
       <c r="G185" t="s">
@@ -4598,7 +4601,7 @@
         <v>30</v>
       </c>
       <c r="E186" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F186" s="6"/>
       <c r="G186" t="s">
@@ -4617,7 +4620,7 @@
         <v>30</v>
       </c>
       <c r="E187" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" t="s">
@@ -4636,7 +4639,7 @@
         <v>30</v>
       </c>
       <c r="E188" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F188" s="6"/>
       <c r="G188" t="s">
@@ -4655,7 +4658,7 @@
         <v>30</v>
       </c>
       <c r="E189" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F189" s="6"/>
       <c r="G189" t="s">
@@ -4674,7 +4677,7 @@
         <v>30</v>
       </c>
       <c r="E190" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F190" s="6"/>
       <c r="G190" t="s">
@@ -4693,7 +4696,7 @@
         <v>30</v>
       </c>
       <c r="E191" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F191" s="6"/>
       <c r="G191" t="s">
@@ -4712,7 +4715,7 @@
         <v>30</v>
       </c>
       <c r="E192" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F192" s="6"/>
       <c r="G192" t="s">
@@ -4731,7 +4734,7 @@
         <v>30</v>
       </c>
       <c r="E193" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F193" s="6"/>
       <c r="G193" t="s">
@@ -4750,7 +4753,7 @@
         <v>30</v>
       </c>
       <c r="E194" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F194" s="6"/>
       <c r="G194" t="s">
@@ -4769,7 +4772,7 @@
         <v>30</v>
       </c>
       <c r="E195" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F195" s="6"/>
       <c r="G195" t="s">
@@ -4788,7 +4791,7 @@
         <v>30</v>
       </c>
       <c r="E196" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F196" s="6"/>
       <c r="G196" t="s">
@@ -4807,7 +4810,7 @@
         <v>30</v>
       </c>
       <c r="E197" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F197" s="6"/>
       <c r="G197" t="s">
@@ -4826,7 +4829,7 @@
         <v>30</v>
       </c>
       <c r="E198" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F198" s="6"/>
       <c r="G198" t="s">
@@ -4845,7 +4848,7 @@
         <v>30</v>
       </c>
       <c r="E199" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F199" s="6"/>
       <c r="G199" t="s">
@@ -4864,7 +4867,7 @@
         <v>30</v>
       </c>
       <c r="E200" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F200" s="6"/>
       <c r="G200" t="s">

--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5367C6-4DD8-412E-93F6-8A84D2254215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B77B64-83DE-46B3-8A6F-E2D5973C1428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="64">
   <si>
     <t>Όνομα μέλους</t>
   </si>
@@ -195,6 +195,30 @@
   </si>
   <si>
     <t xml:space="preserve">ΜΕΛΟΣ </t>
+  </si>
+  <si>
+    <t>Petra Tzo</t>
+  </si>
+  <si>
+    <t>oetratzogua@gmail.com</t>
+  </si>
+  <si>
+    <t>VOUDIOTIS MILTIADIS</t>
+  </si>
+  <si>
+    <t>Αλίκη Ρίγλη</t>
+  </si>
+  <si>
+    <t>KAMMA SOFIA</t>
+  </si>
+  <si>
+    <t>miltosvoudiotis@gmail.com</t>
+  </si>
+  <si>
+    <t>arigli1@yahoo.gr</t>
+  </si>
+  <si>
+    <t>kammasofia@yahoo.com</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1477,7 @@
       </c>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>51</v>
       </c>
@@ -1481,13 +1505,21 @@
       <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>56</v>
+      </c>
       <c r="C22" t="s">
         <v>30</v>
       </c>
+      <c r="D22" s="8">
+        <v>46034</v>
+      </c>
       <c r="E22" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="6"/>
+      <c r="F22" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G22" t="s">
         <v>30</v>
       </c>
@@ -1499,14 +1531,22 @@
       </c>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
+      <c r="D23" s="8">
+        <v>46035</v>
+      </c>
       <c r="E23" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="6"/>
+      <c r="F23" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="G23" t="s">
         <v>30</v>
       </c>
@@ -1518,14 +1558,22 @@
       </c>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="C24" t="s">
         <v>30</v>
       </c>
+      <c r="D24" s="8">
+        <v>46035</v>
+      </c>
       <c r="E24" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="6"/>
+      <c r="F24" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="G24" t="s">
         <v>30</v>
       </c>
@@ -1538,13 +1586,21 @@
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
+      <c r="D25" s="8">
+        <v>46035</v>
+      </c>
       <c r="E25" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="6"/>
+      <c r="F25" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="G25" t="s">
         <v>30</v>
       </c>
@@ -4918,15 +4974,19 @@
     <hyperlink ref="A19" r:id="rId16" display="https://aristonwashdry.gr/admin/users/18" xr:uid="{F4A2EBE6-FF22-4EDC-992D-D2B3F65000A1}"/>
     <hyperlink ref="A20" r:id="rId17" display="https://aristonwashdry.gr/admin/users/19" xr:uid="{CE1D70E6-FBF5-43BC-A9FD-801279D120D7}"/>
     <hyperlink ref="A21" r:id="rId18" display="https://aristonwashdry.gr/admin/users/20" xr:uid="{F319D8B6-A628-4303-A453-A2A9C096D4E8}"/>
+    <hyperlink ref="A22" r:id="rId19" display="https://aristonwashdry.gr/admin/users/21" xr:uid="{9DC58BDB-1B3D-44E4-8DF5-29F0E12C9A88}"/>
+    <hyperlink ref="A23" r:id="rId20" display="https://aristonwashdry.gr/admin/users/22" xr:uid="{424361F0-C923-4090-B22A-8D929733C462}"/>
+    <hyperlink ref="A24" r:id="rId21" display="https://aristonwashdry.gr/admin/users/23" xr:uid="{2B0BBC98-57C8-4B3A-9FD0-B376E28BDB15}"/>
+    <hyperlink ref="A25" r:id="rId22" display="https://aristonwashdry.gr/admin/users/24" xr:uid="{1EA05C9D-D2C1-4E32-B83A-076353DAF0E0}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId19"/>
+  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId23"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId24"/>
   </tableParts>
 </worksheet>
 </file>
--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B77B64-83DE-46B3-8A6F-E2D5973C1428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF1100D-FDD6-40BE-B0EA-93E6FA977CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF1100D-FDD6-40BE-B0EA-93E6FA977CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2771A5-5940-4280-8DFB-1FCC1645F0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="72">
   <si>
     <t>Όνομα μέλους</t>
   </si>
@@ -219,6 +219,30 @@
   </si>
   <si>
     <t>kammasofia@yahoo.com</t>
+  </si>
+  <si>
+    <t>Σταύρος</t>
+  </si>
+  <si>
+    <t>stauroskarras@icloud.com</t>
+  </si>
+  <si>
+    <t>antonis</t>
+  </si>
+  <si>
+    <t>cubotkonst@gmail.com</t>
+  </si>
+  <si>
+    <t>ΖΑΧΑΡΗ ΧΡΥΣΟΥΛΑ</t>
+  </si>
+  <si>
+    <t>chryza_samos@hotmail.com</t>
+  </si>
+  <si>
+    <t>ΓΙΩΡΓΟΣ ΧΡΙΣΤΟΔΟΥΛΑΚΗΣ</t>
+  </si>
+  <si>
+    <t>christod@sch.gr</t>
   </si>
 </sst>
 </file>
@@ -1613,13 +1637,21 @@
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>64</v>
+      </c>
       <c r="C26" t="s">
         <v>30</v>
       </c>
+      <c r="D26" s="8">
+        <v>46036</v>
+      </c>
       <c r="E26" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="F26" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="G26" t="s">
         <v>30</v>
       </c>
@@ -1631,14 +1663,22 @@
       </c>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
+      <c r="D27" s="8">
+        <v>46037</v>
+      </c>
       <c r="E27" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="F27" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="G27" t="s">
         <v>30</v>
       </c>
@@ -1650,14 +1690,22 @@
       </c>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C28" t="s">
         <v>30</v>
       </c>
+      <c r="D28" s="8">
+        <v>46038</v>
+      </c>
       <c r="E28" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="F28" s="11" t="s">
+        <v>69</v>
+      </c>
       <c r="G28" t="s">
         <v>30</v>
       </c>
@@ -1670,13 +1718,21 @@
       <c r="L28" s="6"/>
     </row>
     <row r="29" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="C29" t="s">
         <v>30</v>
       </c>
+      <c r="D29" s="8">
+        <v>46038</v>
+      </c>
       <c r="E29" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="6"/>
+      <c r="F29" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="G29" t="s">
         <v>30</v>
       </c>
@@ -4978,15 +5034,19 @@
     <hyperlink ref="A23" r:id="rId20" display="https://aristonwashdry.gr/admin/users/22" xr:uid="{424361F0-C923-4090-B22A-8D929733C462}"/>
     <hyperlink ref="A24" r:id="rId21" display="https://aristonwashdry.gr/admin/users/23" xr:uid="{2B0BBC98-57C8-4B3A-9FD0-B376E28BDB15}"/>
     <hyperlink ref="A25" r:id="rId22" display="https://aristonwashdry.gr/admin/users/24" xr:uid="{1EA05C9D-D2C1-4E32-B83A-076353DAF0E0}"/>
+    <hyperlink ref="A26" r:id="rId23" display="https://aristonwashdry.gr/admin/users/25" xr:uid="{E037CB8A-369A-41BA-9375-D58657095ECF}"/>
+    <hyperlink ref="A27" r:id="rId24" display="https://aristonwashdry.gr/admin/users/26" xr:uid="{9A63AA3C-6810-4DDC-A6F9-4124CB764198}"/>
+    <hyperlink ref="A28" r:id="rId25" display="https://aristonwashdry.gr/admin/users/27" xr:uid="{2E7B9671-EBCD-43FC-9F81-743195FAA25B}"/>
+    <hyperlink ref="A29" r:id="rId26" display="https://aristonwashdry.gr/admin/users/28" xr:uid="{3B9F3F50-80F2-48C5-B49E-23F0B2CF39BF}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId23"/>
+  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId27"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId24"/>
+    <tablePart r:id="rId28"/>
   </tableParts>
 </worksheet>
 </file>
--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2771A5-5940-4280-8DFB-1FCC1645F0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4F61EA-E7CE-4FAF-9159-885EE252570C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="76">
   <si>
     <t>Όνομα μέλους</t>
   </si>
@@ -243,6 +243,18 @@
   </si>
   <si>
     <t>christod@sch.gr</t>
+  </si>
+  <si>
+    <t>Euripides charalampous</t>
+  </si>
+  <si>
+    <t>euripidescharalampous0@gmail.com</t>
+  </si>
+  <si>
+    <t>andreas tsesmelis</t>
+  </si>
+  <si>
+    <t>antreaskko@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1744,14 +1756,22 @@
       </c>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="C30" t="s">
         <v>30</v>
       </c>
+      <c r="D30" s="8">
+        <v>46042</v>
+      </c>
       <c r="E30" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="6"/>
+      <c r="F30" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="G30" t="s">
         <v>30</v>
       </c>
@@ -1764,13 +1784,21 @@
       <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="C31" t="s">
         <v>30</v>
       </c>
+      <c r="D31" s="8">
+        <v>46043</v>
+      </c>
       <c r="E31" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="6"/>
+      <c r="F31" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="G31" t="s">
         <v>30</v>
       </c>
@@ -5038,15 +5066,17 @@
     <hyperlink ref="A27" r:id="rId24" display="https://aristonwashdry.gr/admin/users/26" xr:uid="{9A63AA3C-6810-4DDC-A6F9-4124CB764198}"/>
     <hyperlink ref="A28" r:id="rId25" display="https://aristonwashdry.gr/admin/users/27" xr:uid="{2E7B9671-EBCD-43FC-9F81-743195FAA25B}"/>
     <hyperlink ref="A29" r:id="rId26" display="https://aristonwashdry.gr/admin/users/28" xr:uid="{3B9F3F50-80F2-48C5-B49E-23F0B2CF39BF}"/>
+    <hyperlink ref="A30" r:id="rId27" display="https://aristonwashdry.gr/admin/users/30" xr:uid="{346B7075-C82A-499B-8751-F6D978CE0D65}"/>
+    <hyperlink ref="A31" r:id="rId28" display="https://aristonwashdry.gr/admin/users/31" xr:uid="{9FD4251F-EAE6-46FB-B380-2705DFC43357}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId27"/>
+  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId29"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId28"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>
--- a/members.xlsx
+++ b/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4F61EA-E7CE-4FAF-9159-885EE252570C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22ADDD60-95F6-4FAB-93E8-6159E335FF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="78">
   <si>
     <t>Όνομα μέλους</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>antreaskko@gmail.com</t>
+  </si>
+  <si>
+    <t>Μαρίνα Κυπραίου</t>
+  </si>
+  <si>
+    <t>manina_kyp@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -1783,7 +1789,7 @@
       </c>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>74</v>
       </c>
@@ -1811,13 +1817,21 @@
       <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="C32" t="s">
         <v>30</v>
       </c>
+      <c r="D32" s="8">
+        <v>46043</v>
+      </c>
       <c r="E32" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="6"/>
+      <c r="F32" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="G32" t="s">
         <v>30</v>
       </c>
@@ -5068,15 +5082,16 @@
     <hyperlink ref="A29" r:id="rId26" display="https://aristonwashdry.gr/admin/users/28" xr:uid="{3B9F3F50-80F2-48C5-B49E-23F0B2CF39BF}"/>
     <hyperlink ref="A30" r:id="rId27" display="https://aristonwashdry.gr/admin/users/30" xr:uid="{346B7075-C82A-499B-8751-F6D978CE0D65}"/>
     <hyperlink ref="A31" r:id="rId28" display="https://aristonwashdry.gr/admin/users/31" xr:uid="{9FD4251F-EAE6-46FB-B380-2705DFC43357}"/>
+    <hyperlink ref="A32" r:id="rId29" display="https://aristonwashdry.gr/admin/users/32" xr:uid="{DE3F359F-C498-4809-BAAA-3053ADEAA31B}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId29"/>
+  <pageSetup scale="48" fitToHeight="0" orientation="landscape" r:id="rId30"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>